--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -2191,7 +2191,7 @@
         <v>136413950</v>
       </c>
       <c r="B13" t="n">
-        <v>107053</v>
+        <v>107056</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136413953</v>
       </c>
       <c r="B14" t="n">
-        <v>107053</v>
+        <v>107056</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136413956</v>
       </c>
       <c r="B15" t="n">
-        <v>107053</v>
+        <v>107056</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -2191,7 +2191,7 @@
         <v>136413950</v>
       </c>
       <c r="B13" t="n">
-        <v>107056</v>
+        <v>107057</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136413953</v>
       </c>
       <c r="B14" t="n">
-        <v>107056</v>
+        <v>107057</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136413956</v>
       </c>
       <c r="B15" t="n">
-        <v>107056</v>
+        <v>107057</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -2191,7 +2191,7 @@
         <v>136413950</v>
       </c>
       <c r="B13" t="n">
-        <v>107057</v>
+        <v>107062</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136413953</v>
       </c>
       <c r="B14" t="n">
-        <v>107057</v>
+        <v>107062</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136413956</v>
       </c>
       <c r="B15" t="n">
-        <v>107057</v>
+        <v>107062</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -2191,7 +2191,7 @@
         <v>136413950</v>
       </c>
       <c r="B13" t="n">
-        <v>107062</v>
+        <v>107064</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136413953</v>
       </c>
       <c r="B14" t="n">
-        <v>107062</v>
+        <v>107064</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136413956</v>
       </c>
       <c r="B15" t="n">
-        <v>107062</v>
+        <v>107064</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -2191,7 +2191,7 @@
         <v>136413950</v>
       </c>
       <c r="B13" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136413953</v>
       </c>
       <c r="B14" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136413956</v>
       </c>
       <c r="B15" t="n">
-        <v>107064</v>
+        <v>107070</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -2191,7 +2191,7 @@
         <v>136413950</v>
       </c>
       <c r="B13" t="n">
-        <v>107070</v>
+        <v>107072</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136413953</v>
       </c>
       <c r="B14" t="n">
-        <v>107070</v>
+        <v>107072</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136413956</v>
       </c>
       <c r="B15" t="n">
-        <v>107070</v>
+        <v>107072</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>

--- a/artfynd/A 43379-2022 artfynd.xlsx
+++ b/artfynd/A 43379-2022 artfynd.xlsx
@@ -2191,7 +2191,7 @@
         <v>136413950</v>
       </c>
       <c r="B13" t="n">
-        <v>107072</v>
+        <v>107073</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -2298,7 +2298,7 @@
         <v>136413953</v>
       </c>
       <c r="B14" t="n">
-        <v>107072</v>
+        <v>107073</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2409,7 +2409,7 @@
         <v>136413956</v>
       </c>
       <c r="B15" t="n">
-        <v>107072</v>
+        <v>107073</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
